--- a/LaTeXTemplate/author.xlsx
+++ b/LaTeXTemplate/author.xlsx
@@ -1,29 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Wings-Hub\ML24\ML24-EX01-KeywordSpotting\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ninab\Documents\Studium\Semester_4\AT\eigeneSammlung\LaTeXTemplate\LaTeXTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD19006-5E7D-44DA-9D96-A053E3D0AAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="15960" windowHeight="18075"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Project" sheetId="2" r:id="rId2"/>
     <sheet name="Student 1" sheetId="3" r:id="rId3"/>
     <sheet name="Student 2" sheetId="4" r:id="rId4"/>
-    <sheet name="Student 3" sheetId="5" r:id="rId5"/>
+    <sheet name="Student 3" sheetId="8" r:id="rId5"/>
+    <sheet name="Student 4" sheetId="7" r:id="rId6"/>
+    <sheet name="Student 5" sheetId="9" r:id="rId7"/>
+    <sheet name="wings" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="96">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -86,9 +90,6 @@
     <t>Study Course:</t>
   </si>
   <si>
-    <t>Business Intelligen ans Data Analytics</t>
-  </si>
-  <si>
     <t>Semester:</t>
   </si>
   <si>
@@ -117,12 +118,6 @@
   </si>
   <si>
     <t>Company name/Department:</t>
-  </si>
-  <si>
-    <t>Hochschule Emden</t>
-  </si>
-  <si>
-    <t>Department of Technology</t>
   </si>
   <si>
     <t>&lt;Mechanical Engineering Department&gt;</t>
@@ -208,9 +203,6 @@
     <t>Student 2</t>
   </si>
   <si>
-    <t>ML &amp; Project T</t>
-  </si>
-  <si>
     <t>&lt;Hochschule Emden/Leer&gt; or &lt; VW Wolfsburg&gt; or &lt;...&gt;</t>
   </si>
   <si>
@@ -239,12 +231,108 @@
   </si>
   <si>
     <t>ML24-04 Keyword Spotting with an Arduino Nano 33 BLE Sense</t>
+  </si>
+  <si>
+    <t>Carl Lewis</t>
+  </si>
+  <si>
+    <t>Maschke</t>
+  </si>
+  <si>
+    <t>DejaVure</t>
+  </si>
+  <si>
+    <t>Maschinenbau und Design</t>
+  </si>
+  <si>
+    <t>Automatisierungstechnik</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>valeriia.kornichenkova@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>asena.yuece@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>carl.lewis.maschke@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>Valeriia679</t>
+  </si>
+  <si>
+    <t>sven.neumann@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>nina.braams@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>Nina</t>
+  </si>
+  <si>
+    <t>Braams</t>
+  </si>
+  <si>
+    <t>NB-Stud</t>
+  </si>
+  <si>
+    <t>nina.braams@ewe.net</t>
+  </si>
+  <si>
+    <t>Sven586</t>
+  </si>
+  <si>
+    <t>30.05.2003</t>
+  </si>
+  <si>
+    <t>Sven</t>
+  </si>
+  <si>
+    <t>Neumann</t>
+  </si>
+  <si>
+    <t>09.06.2000</t>
+  </si>
+  <si>
+    <t>07.11.2000</t>
+  </si>
+  <si>
+    <t>26.06.2003</t>
+  </si>
+  <si>
+    <t>02.06.2004</t>
+  </si>
+  <si>
+    <t>Asena</t>
+  </si>
+  <si>
+    <t>Yuece</t>
+  </si>
+  <si>
+    <t>asenaycce</t>
+  </si>
+  <si>
+    <t>Valeriia</t>
+  </si>
+  <si>
+    <t>Kornichenkova</t>
+  </si>
+  <si>
+    <t>Fachbereich Technik</t>
+  </si>
+  <si>
+    <t>Hochschule Emden/Leer</t>
+  </si>
+  <si>
+    <t>26723 Emden</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -358,8 +446,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="24">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -372,41 +460,39 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1537,22 +1623,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="12.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="12.9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="4" width="30.5703125" customWidth="1"/>
+    <col min="2" max="4" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="19" t="s">
+    <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-    </row>
-    <row r="7" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+    </row>
+    <row r="7" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1563,14 +1649,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
         <v>5</v>
@@ -1579,14 +1665,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
         <v>5</v>
@@ -1595,36 +1681,36 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1632,49 +1718,49 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D10" location="'Project'!R1C1" display="Project"/>
-    <hyperlink ref="D12" location="'Student 1'!R1C1" display="Student 1"/>
-    <hyperlink ref="D14" location="'Student 2'!R1C1" display="Student 2"/>
-    <hyperlink ref="D16" location="'Student 3'!R1C1" display="Student 3"/>
+    <hyperlink ref="D10" location="'Project'!R1C1" display="Project" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D12" location="'Student 1'!R1C1" display="Student 1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D14" location="'Student 2'!R1C1" display="Student 2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D16" location="'Student 3'!R1C1" display="Student 3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="5" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="24.88671875" style="5" customWidth="1"/>
+    <col min="2" max="6" width="11.44140625" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="61.9" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
     </row>
-    <row r="3" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
@@ -1683,16 +1769,16 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
@@ -1701,30 +1787,30 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
-        <v>67</v>
+    <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1737,7 +1823,7 @@
     <mergeCell ref="A5:C5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1"/>
+    <hyperlink ref="A7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740200000000005" bottom="0.78740200000000005" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -1748,20 +1834,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="43.85546875" style="9" customWidth="1"/>
-    <col min="6" max="7" width="8.85546875" style="9" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="9"/>
+    <col min="1" max="1" width="47.33203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="43.88671875" style="5" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1769,7 +1855,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1777,8 +1863,8 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="6"/>
@@ -1787,7 +1873,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -1807,23 +1893,33 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="10">
+        <v>7024640</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="12"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1831,19 +1927,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1851,17 +1947,19 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="B10" s="12">
+        <v>4</v>
+      </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1869,27 +1967,31 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="14"/>
+        <v>20</v>
+      </c>
+      <c r="B12" s="13">
+        <v>45730</v>
+      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="B13" s="13">
+        <v>45831</v>
+      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1897,29 +1999,31 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="13">
-        <v>10</v>
+        <v>23</v>
+      </c>
+      <c r="B16" s="12">
+        <v>5</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1927,7 +2031,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1935,17 +2039,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="8"/>
+        <v>24</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1953,9 +2059,9 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
-        <v>26</v>
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="14" t="s">
+        <v>25</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1963,9 +2069,9 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="6"/>
@@ -1973,9 +2079,9 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="6"/>
@@ -1983,71 +2089,69 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
+      <c r="B24" s="8"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
-      <c r="B27" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="B27" s="8"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2055,7 +2159,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2063,9 +2167,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2073,9 +2177,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -2083,9 +2187,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -2093,9 +2197,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -2103,17 +2207,17 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="15" t="s">
-        <v>44</v>
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -2121,69 +2225,69 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="16"/>
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16"/>
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="15" t="s">
-        <v>50</v>
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="14" t="s">
+        <v>47</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -2191,64 +2295,64 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="16"/>
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -2257,12 +2361,13 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Technical Management,Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B40" r:id="rId1"/>
+    <hyperlink ref="B40" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{4236688E-1B7A-4D30-90BF-0ED3EA43D8F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -2273,21 +2378,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" style="17" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="17" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="44.42578125" style="17" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="17" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="17" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="17"/>
+    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2295,7 +2400,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2303,8 +2408,8 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="6"/>
@@ -2313,7 +2418,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -2333,23 +2438,33 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="10">
+        <v>7024769</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>70</v>
+      </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="12"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2357,19 +2472,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -2377,19 +2492,19 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="13">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="B10" s="12">
+        <v>4</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -2397,27 +2512,31 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="14"/>
+        <v>20</v>
+      </c>
+      <c r="B12" s="13">
+        <v>45730</v>
+      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="B13" s="13">
+        <v>45831</v>
+      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -2425,31 +2544,31 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="13">
-        <v>10</v>
+        <v>23</v>
+      </c>
+      <c r="B16" s="12">
+        <v>5</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2457,7 +2576,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -2465,17 +2584,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="8"/>
+        <v>24</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>85</v>
+      </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -2483,9 +2604,9 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
-        <v>26</v>
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="14" t="s">
+        <v>25</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2493,27 +2614,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="8"/>
+        <v>26</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="8"/>
+        <v>27</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2521,63 +2646,61 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
-      <c r="B27" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="B27" s="8"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2585,7 +2708,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2593,9 +2716,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2603,9 +2726,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -2613,9 +2736,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -2623,9 +2746,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -2633,17 +2756,17 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="15" t="s">
-        <v>44</v>
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -2651,69 +2774,69 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="16"/>
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16"/>
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="15" t="s">
-        <v>50</v>
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="14" t="s">
+        <v>47</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -2721,64 +2844,64 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="16"/>
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -2787,12 +2910,13 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Technical Management,Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B40" r:id="rId1"/>
+    <hyperlink ref="B40" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{52CD9D29-2861-4E48-92CB-3B711FEEAE53}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740200000000005" bottom="0.78740200000000005" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -2803,19 +2927,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC551AE2-232B-4F37-A6D5-76CE042A5043}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.140625" style="18" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" style="18" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="18" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" style="18" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" style="18" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="18"/>
+    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2823,7 +2949,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2831,8 +2957,8 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="6"/>
@@ -2841,7 +2967,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -2861,29 +2987,33 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="11">
-        <v>1234567</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="C5" s="10">
+        <v>7024749</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="12"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2891,17 +3021,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -2909,19 +3041,19 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="13">
-        <v>7</v>
+        <v>19</v>
+      </c>
+      <c r="B10" s="12">
+        <v>4</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -2929,31 +3061,31 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="14">
-        <v>45351</v>
+        <v>20</v>
+      </c>
+      <c r="B12" s="13">
+        <v>45730</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="14">
-        <v>45594</v>
+        <v>21</v>
+      </c>
+      <c r="B13" s="13">
+        <v>45831</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -2961,29 +3093,31 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>63</v>
+        <v>23</v>
+      </c>
+      <c r="B16" s="12">
+        <v>5</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2991,7 +3125,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -2999,19 +3133,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3019,9 +3153,9 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
-        <v>26</v>
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="14" t="s">
+        <v>25</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -3029,31 +3163,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3061,63 +3195,61 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
-      <c r="B27" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="B27" s="8"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -3125,7 +3257,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -3133,9 +3265,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -3143,53 +3275,47 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>39</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B33" s="8"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>41</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B34" s="8"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>43</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B35" s="8"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="15" t="s">
-        <v>44</v>
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -3197,69 +3323,69 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="16"/>
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16"/>
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="15" t="s">
-        <v>50</v>
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="14" t="s">
+        <v>47</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3267,64 +3393,64 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="16"/>
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -3333,7 +3459,1655 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{0E0B3E66-8EBF-4E5D-A0CA-E10BEAD90619}">
+      <formula1>"Technical Management,Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B40" r:id="rId1" xr:uid="{1DF4AA0A-AD69-4965-B5BA-56F8A5F06FCF}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{3F915F7C-720A-411C-801F-1717546B05F4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.78740200000000005" bottom="0.78740200000000005" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{283BD7E5-E0D0-4A6A-B1D5-0C7015D88B45}">
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="10">
+        <v>7025068</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="12">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="13">
+        <v>45730</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="13">
+        <v>45831</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="12">
+        <v>5</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="15"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="15"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="15"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="15"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="15"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{973FB696-E482-42B8-9C00-226E2B1112C9}">
+      <formula1>"Technical Management,Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B40" r:id="rId1" xr:uid="{FF397962-62D2-4E0D-8E98-B0C2BA2943AD}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{58E67571-A71B-46D9-A9F7-BAD5B0558177}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.78740200000000005" bottom="0.78740200000000005" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB98D58-38D8-4A44-9926-B20EEA7E6B71}">
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="10">
+        <v>7024847</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="12">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="13">
+        <v>45730</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="13">
+        <v>45831</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="12">
+        <v>5</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="15"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="15"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="15"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="15"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="15"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{8CB2F039-9A17-493E-8A92-AA3DC5EA8AAE}">
+      <formula1>"Technical Management,Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B40" r:id="rId1" xr:uid="{3929AC92-7317-4625-8D7C-ED71E59994A1}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{F7B263C3-8A7E-4844-96BB-766526D73D67}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{F8DDB6CC-9BA1-4FCF-92A0-767251BF6D91}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.78740200000000005" bottom="0.78740200000000005" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="5" customWidth="1"/>
+    <col min="4" max="5" width="16.109375" style="5" customWidth="1"/>
+    <col min="6" max="7" width="11.44140625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1234567</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="12">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="13">
+        <v>45351</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="13">
+        <v>45594</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="15"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="15"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="15"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="15"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="15"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Technical Management,Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/LaTeXTemplate/author.xlsx
+++ b/LaTeXTemplate/author.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ninab\Documents\Studium\Semester_4\AT\eigeneSammlung\LaTeXTemplate\LaTeXTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD19006-5E7D-44DA-9D96-A053E3D0AAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A10BBC-AC83-49BD-90B9-5451CE61A489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="98">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>26723 Emden</t>
+  </si>
+  <si>
+    <t>26725 Emden</t>
+  </si>
+  <si>
+    <t>Friedrich-Ebert-Straße 1-3</t>
   </si>
 </sst>
 </file>
@@ -476,6 +482,7 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -492,7 +499,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1625,20 +1631,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="12.9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="12.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="4" width="30.5546875" customWidth="1"/>
+    <col min="2" max="4" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+    <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-    </row>
-    <row r="7" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+    </row>
+    <row r="7" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1649,14 +1655,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
         <v>5</v>
@@ -1665,14 +1671,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
         <v>5</v>
@@ -1681,14 +1687,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
         <v>5</v>
@@ -1697,14 +1703,14 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
         <v>5</v>
@@ -1730,37 +1736,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.88671875" style="5" customWidth="1"/>
-    <col min="2" max="6" width="11.44140625" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="5"/>
+    <col min="1" max="1" width="24.85546875" style="5" customWidth="1"/>
+    <col min="2" max="6" width="11.42578125" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:5" ht="61.9" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
     </row>
-    <row r="3" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
@@ -1769,16 +1775,16 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
@@ -1787,7 +1793,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>63</v>
       </c>
@@ -1796,21 +1802,21 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1836,18 +1842,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.33203125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="33.109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="43.88671875" style="5" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="47.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="43.85546875" style="5" customWidth="1"/>
+    <col min="6" max="7" width="8.85546875" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1855,7 +1861,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1863,7 +1869,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
@@ -1873,7 +1879,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -1893,7 +1899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
@@ -1906,12 +1912,12 @@
       <c r="D5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="17" t="s">
         <v>72</v>
       </c>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -1919,7 +1925,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1927,7 +1933,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
@@ -1939,7 +1945,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1947,7 +1953,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -1959,7 +1965,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1967,7 +1973,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -1979,7 +1985,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>21</v>
       </c>
@@ -1991,7 +1997,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1999,7 +2005,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
@@ -2011,7 +2017,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>23</v>
       </c>
@@ -2023,7 +2029,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2031,7 +2037,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -2039,7 +2045,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>24</v>
       </c>
@@ -2051,7 +2057,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -2059,7 +2065,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
@@ -2069,7 +2075,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
@@ -2079,7 +2085,7 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>27</v>
       </c>
@@ -2089,7 +2095,7 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="8"/>
       <c r="C24" s="6"/>
@@ -2097,7 +2103,7 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>28</v>
       </c>
@@ -2109,7 +2115,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
         <v>93</v>
@@ -2119,7 +2125,7 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -2127,7 +2133,7 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>30</v>
       </c>
@@ -2139,7 +2145,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>32</v>
       </c>
@@ -2151,7 +2157,7 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2159,7 +2165,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2167,7 +2173,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
@@ -2177,7 +2183,7 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>35</v>
       </c>
@@ -2187,7 +2193,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
@@ -2197,7 +2203,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>39</v>
       </c>
@@ -2207,7 +2213,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -2215,7 +2221,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>41</v>
       </c>
@@ -2225,7 +2231,7 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>42</v>
       </c>
@@ -2237,7 +2243,7 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>34</v>
       </c>
@@ -2249,7 +2255,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>45</v>
       </c>
@@ -2261,7 +2267,7 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2269,7 +2275,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2277,7 +2283,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2285,7 +2291,7 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>47</v>
       </c>
@@ -2295,7 +2301,7 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>42</v>
       </c>
@@ -2307,7 +2313,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>34</v>
       </c>
@@ -2319,7 +2325,7 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>45</v>
       </c>
@@ -2331,7 +2337,7 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2339,7 +2345,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2347,7 +2353,7 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>51</v>
       </c>
@@ -2380,19 +2386,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="5"/>
+    <col min="1" max="1" width="29.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2400,7 +2406,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2408,7 +2414,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
@@ -2418,7 +2424,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -2438,7 +2444,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>91</v>
       </c>
@@ -2451,12 +2457,12 @@
       <c r="D5" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="17" t="s">
         <v>70</v>
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -2464,7 +2470,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2472,7 +2478,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
@@ -2484,7 +2490,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -2492,7 +2498,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -2504,7 +2510,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -2512,7 +2518,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -2524,7 +2530,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>21</v>
       </c>
@@ -2536,7 +2542,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -2544,7 +2550,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
@@ -2556,7 +2562,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>23</v>
       </c>
@@ -2568,7 +2574,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2576,7 +2582,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -2584,7 +2590,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>24</v>
       </c>
@@ -2596,7 +2602,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -2604,7 +2610,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
@@ -2614,7 +2620,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
@@ -2626,7 +2632,7 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>27</v>
       </c>
@@ -2638,7 +2644,7 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2646,7 +2652,7 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>28</v>
       </c>
@@ -2658,7 +2664,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
         <v>93</v>
@@ -2668,7 +2674,7 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -2676,7 +2682,7 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>30</v>
       </c>
@@ -2688,7 +2694,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>32</v>
       </c>
@@ -2700,7 +2706,7 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2708,7 +2714,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2716,7 +2722,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
@@ -2726,7 +2732,7 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>35</v>
       </c>
@@ -2736,7 +2742,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
@@ -2746,7 +2752,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>39</v>
       </c>
@@ -2756,7 +2762,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -2764,7 +2770,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>41</v>
       </c>
@@ -2774,7 +2780,7 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>42</v>
       </c>
@@ -2786,7 +2792,7 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>34</v>
       </c>
@@ -2798,7 +2804,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>45</v>
       </c>
@@ -2810,7 +2816,7 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2818,7 +2824,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2826,7 +2832,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2834,7 +2840,7 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>47</v>
       </c>
@@ -2844,7 +2850,7 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>42</v>
       </c>
@@ -2856,7 +2862,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>34</v>
       </c>
@@ -2868,7 +2874,7 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>45</v>
       </c>
@@ -2880,7 +2886,7 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2888,7 +2894,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2896,7 +2902,7 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>51</v>
       </c>
@@ -2929,19 +2935,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC551AE2-232B-4F37-A6D5-76CE042A5043}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="5"/>
+    <col min="1" max="1" width="29.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2949,7 +2955,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2957,7 +2963,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
@@ -2967,7 +2973,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -2987,7 +2993,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>88</v>
       </c>
@@ -3000,12 +3006,12 @@
       <c r="D5" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="17" t="s">
         <v>71</v>
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -3013,7 +3019,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3021,7 +3027,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
@@ -3033,7 +3039,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -3041,7 +3047,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -3053,7 +3059,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -3061,7 +3067,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -3073,7 +3079,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>21</v>
       </c>
@@ -3085,7 +3091,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -3093,7 +3099,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
@@ -3105,7 +3111,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>23</v>
       </c>
@@ -3117,7 +3123,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -3125,7 +3131,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -3133,7 +3139,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>24</v>
       </c>
@@ -3145,7 +3151,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3153,7 +3159,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
@@ -3163,7 +3169,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
@@ -3175,7 +3181,7 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>27</v>
       </c>
@@ -3187,7 +3193,7 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3195,7 +3201,7 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>28</v>
       </c>
@@ -3207,7 +3213,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
         <v>93</v>
@@ -3217,7 +3223,7 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -3225,7 +3231,7 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>30</v>
       </c>
@@ -3237,7 +3243,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>32</v>
       </c>
@@ -3249,7 +3255,7 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -3257,7 +3263,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -3265,7 +3271,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
@@ -3275,7 +3281,7 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>35</v>
       </c>
@@ -3285,7 +3291,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
@@ -3295,7 +3301,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>39</v>
       </c>
@@ -3305,7 +3311,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -3313,7 +3319,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>41</v>
       </c>
@@ -3323,7 +3329,7 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>42</v>
       </c>
@@ -3335,7 +3341,7 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>34</v>
       </c>
@@ -3347,7 +3353,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>45</v>
       </c>
@@ -3359,7 +3365,7 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3367,7 +3373,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -3375,7 +3381,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -3383,7 +3389,7 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>47</v>
       </c>
@@ -3393,7 +3399,7 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>42</v>
       </c>
@@ -3405,7 +3411,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>34</v>
       </c>
@@ -3417,7 +3423,7 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>45</v>
       </c>
@@ -3429,7 +3435,7 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -3437,7 +3443,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3445,7 +3451,7 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>51</v>
       </c>
@@ -3478,19 +3484,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{283BD7E5-E0D0-4A6A-B1D5-0C7015D88B45}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="5"/>
+    <col min="1" max="1" width="29.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3498,7 +3504,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3506,7 +3512,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
@@ -3516,7 +3522,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -3536,7 +3542,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>82</v>
       </c>
@@ -3549,12 +3555,12 @@
       <c r="D5" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="17" t="s">
         <v>74</v>
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -3562,7 +3568,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3570,7 +3576,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
@@ -3582,7 +3588,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -3590,7 +3596,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -3602,7 +3608,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -3610,7 +3616,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -3622,7 +3628,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>21</v>
       </c>
@@ -3634,7 +3640,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -3642,7 +3648,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
@@ -3654,7 +3660,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>23</v>
       </c>
@@ -3666,7 +3672,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -3674,7 +3680,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -3682,7 +3688,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>24</v>
       </c>
@@ -3694,7 +3700,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3702,7 +3708,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
@@ -3712,7 +3718,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
@@ -3724,7 +3730,7 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>27</v>
       </c>
@@ -3736,7 +3742,7 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3744,7 +3750,7 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>28</v>
       </c>
@@ -3756,7 +3762,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
         <v>93</v>
@@ -3766,7 +3772,7 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -3774,7 +3780,7 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>30</v>
       </c>
@@ -3786,7 +3792,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>32</v>
       </c>
@@ -3798,7 +3804,7 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -3806,7 +3812,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -3814,7 +3820,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
@@ -3824,7 +3830,7 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>35</v>
       </c>
@@ -3834,7 +3840,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
@@ -3844,7 +3850,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>39</v>
       </c>
@@ -3854,7 +3860,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -3862,7 +3868,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>41</v>
       </c>
@@ -3872,7 +3878,7 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>42</v>
       </c>
@@ -3884,7 +3890,7 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>34</v>
       </c>
@@ -3896,7 +3902,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>45</v>
       </c>
@@ -3908,7 +3914,7 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3916,7 +3922,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -3924,7 +3930,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -3932,7 +3938,7 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>47</v>
       </c>
@@ -3942,7 +3948,7 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>42</v>
       </c>
@@ -3954,7 +3960,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>34</v>
       </c>
@@ -3966,7 +3972,7 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>45</v>
       </c>
@@ -3978,7 +3984,7 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -3986,7 +3992,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3994,7 +4000,7 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>51</v>
       </c>
@@ -4027,19 +4033,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB98D58-38D8-4A44-9926-B20EEA7E6B71}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="5"/>
+    <col min="1" max="1" width="29.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4047,7 +4053,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -4055,7 +4061,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
@@ -4065,7 +4071,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -4085,7 +4091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>76</v>
       </c>
@@ -4098,14 +4104,14 @@
       <c r="D5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="17" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -4113,7 +4119,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4121,7 +4127,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
@@ -4133,7 +4139,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -4141,7 +4147,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -4153,7 +4159,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4161,7 +4167,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -4173,7 +4179,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>21</v>
       </c>
@@ -4185,7 +4191,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -4193,7 +4199,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
@@ -4205,7 +4211,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>23</v>
       </c>
@@ -4217,7 +4223,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -4225,7 +4231,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -4233,7 +4239,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>24</v>
       </c>
@@ -4245,7 +4251,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -4253,7 +4259,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
@@ -4263,31 +4269,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -4295,7 +4301,7 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>28</v>
       </c>
@@ -4307,7 +4313,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
         <v>93</v>
@@ -4317,7 +4323,7 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -4325,7 +4331,7 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>30</v>
       </c>
@@ -4337,7 +4343,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>32</v>
       </c>
@@ -4349,7 +4355,7 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4357,7 +4363,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -4365,7 +4371,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
@@ -4375,7 +4381,7 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>35</v>
       </c>
@@ -4385,7 +4391,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
@@ -4395,7 +4401,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>39</v>
       </c>
@@ -4405,7 +4411,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -4413,7 +4419,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>41</v>
       </c>
@@ -4423,7 +4429,7 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>42</v>
       </c>
@@ -4435,7 +4441,7 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>34</v>
       </c>
@@ -4447,7 +4453,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>45</v>
       </c>
@@ -4459,7 +4465,7 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -4467,7 +4473,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -4475,7 +4481,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -4483,7 +4489,7 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>47</v>
       </c>
@@ -4493,7 +4499,7 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>42</v>
       </c>
@@ -4505,7 +4511,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>34</v>
       </c>
@@ -4517,7 +4523,7 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>45</v>
       </c>
@@ -4529,7 +4535,7 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -4537,7 +4543,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -4545,7 +4551,7 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>51</v>
       </c>
@@ -4579,17 +4585,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="5" customWidth="1"/>
-    <col min="4" max="5" width="16.109375" style="5" customWidth="1"/>
-    <col min="6" max="7" width="11.44140625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="5"/>
+    <col min="1" max="1" width="29.140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="49.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="5" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" style="5" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4597,7 +4603,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -4605,7 +4611,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
@@ -4615,7 +4621,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -4635,7 +4641,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>57</v>
       </c>
@@ -4649,7 +4655,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -4657,7 +4663,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4665,7 +4671,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
@@ -4675,7 +4681,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -4683,7 +4689,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -4695,7 +4701,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4703,7 +4709,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -4715,7 +4721,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>21</v>
       </c>
@@ -4727,7 +4733,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -4735,7 +4741,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
@@ -4745,7 +4751,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>23</v>
       </c>
@@ -4757,7 +4763,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -4765,7 +4771,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -4773,7 +4779,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>24</v>
       </c>
@@ -4785,7 +4791,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -4793,7 +4799,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
@@ -4803,7 +4809,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
@@ -4815,7 +4821,7 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>27</v>
       </c>
@@ -4827,7 +4833,7 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -4835,7 +4841,7 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>28</v>
       </c>
@@ -4847,7 +4853,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
         <v>55</v>
@@ -4857,7 +4863,7 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="8" t="s">
         <v>29</v>
@@ -4867,7 +4873,7 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>30</v>
       </c>
@@ -4879,7 +4885,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>32</v>
       </c>
@@ -4891,7 +4897,7 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4899,7 +4905,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -4907,7 +4913,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
@@ -4917,7 +4923,7 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>35</v>
       </c>
@@ -4929,7 +4935,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
@@ -4941,7 +4947,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>39</v>
       </c>
@@ -4953,7 +4959,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -4961,7 +4967,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>41</v>
       </c>
@@ -4971,7 +4977,7 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>42</v>
       </c>
@@ -4983,7 +4989,7 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>34</v>
       </c>
@@ -4995,7 +5001,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>45</v>
       </c>
@@ -5007,7 +5013,7 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -5015,7 +5021,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -5023,7 +5029,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -5031,7 +5037,7 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>47</v>
       </c>
@@ -5041,7 +5047,7 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>42</v>
       </c>
@@ -5053,7 +5059,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>34</v>
       </c>
@@ -5065,7 +5071,7 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>45</v>
       </c>
@@ -5077,7 +5083,7 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -5085,7 +5091,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -5093,7 +5099,7 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>51</v>
       </c>

--- a/LaTeXTemplate/author.xlsx
+++ b/LaTeXTemplate/author.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ninab\Documents\Studium\Semester_4\AT\eigeneSammlung\LaTeXTemplate\LaTeXTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlm\Documents\LaTeXTemplate\LaTeXTemplate\LaTeXTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A10BBC-AC83-49BD-90B9-5451CE61A489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6444497F-2358-424D-AB92-F4AB7D76A196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Project" sheetId="2" r:id="rId2"/>
+    <sheet name="Projekt" sheetId="2" r:id="rId2"/>
     <sheet name="Student 1" sheetId="3" r:id="rId3"/>
     <sheet name="Student 2" sheetId="4" r:id="rId4"/>
     <sheet name="Student 3" sheetId="8" r:id="rId5"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="98">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -45,19 +45,6 @@
   </si>
   <si>
     <t>Table 1</t>
-  </si>
-  <si>
-    <t>Keyword Spotting with Arduino Nano 33 BLE Sense</t>
-  </si>
-  <si>
-    <t>Short Description</t>
-  </si>
-  <si>
-    <t>In this project, you’ll train a machine learning model to recognize certain keywords
-(e.g., Yes, No). The model is loaded onto your Nano 33 BLE
-board, which has built-in Bluetooth and a microphone—perfect for capturing audio
-input. When the board detects a keyword, it triggers an action, such as blinking an
-LED</t>
   </si>
   <si>
     <t>github Project</t>
@@ -230,9 +217,6 @@
     <t>&lt;Einstein, Albert&gt;</t>
   </si>
   <si>
-    <t>ML24-04 Keyword Spotting with an Arduino Nano 33 BLE Sense</t>
-  </si>
-  <si>
     <t>Carl Lewis</t>
   </si>
   <si>
@@ -333,6 +317,18 @@
   </si>
   <si>
     <t>Friedrich-Ebert-Straße 1-3</t>
+  </si>
+  <si>
+    <t>Magic Faucet Fountain</t>
+  </si>
+  <si>
+    <t>Kursarbeit: Magic Faucet Foutain</t>
+  </si>
+  <si>
+    <t>Kurzbeschreibung</t>
+  </si>
+  <si>
+    <t>Der Magic Faucet Fountain ist die Applikation unserer Kursarbeit. Dabei handelt es sich um einen intelligenten, mittels Smartphone steuerbaren Springbrunnen für den Indoor-Gebrauch. Der Magic Faucet Fountain erzeugt den Effekt, dass ein Wasserhahn auf einer fließenden Wassersäule schwebt.</t>
   </si>
 </sst>
 </file>
@@ -398,7 +394,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -423,8 +419,14 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -447,12 +449,176 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -481,23 +647,61 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1631,20 +1835,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="12.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="12.95" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="4" width="30.5703125" customWidth="1"/>
+    <col min="2" max="4" width="30.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
+    <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-    </row>
-    <row r="7" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+    </row>
+    <row r="7" spans="2:4" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1655,14 +1859,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
         <v>5</v>
@@ -1671,52 +1875,52 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B11" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B15" s="2" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1735,101 +1939,117 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="5" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="24.86328125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="34.9296875" style="5" customWidth="1"/>
+    <col min="4" max="6" width="11.3984375" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="11.3984375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="61.9" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:6" ht="61.9" customHeight="1" x14ac:dyDescent="1">
+      <c r="A1" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="21"/>
+    </row>
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="21"/>
+    </row>
+    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="21"/>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="21"/>
+    </row>
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="21"/>
+    </row>
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="21"/>
+    </row>
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="21"/>
+    </row>
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="A7" r:id="rId1" display="ML24-04 Keyword Spotting with an Arduino Nano 33 BLE Sense" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="A7:C7" r:id="rId2" display="Magic Faucet Fountain" xr:uid="{CAC6622F-02E8-4287-99CF-1AE43AAA30FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740200000000005" bottom="0.78740200000000005" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -1842,18 +2062,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="43.85546875" style="5" customWidth="1"/>
-    <col min="6" max="7" width="8.85546875" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="1" width="47.265625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.86328125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="33.1328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="16.1328125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="43.86328125" style="5" customWidth="1"/>
+    <col min="6" max="7" width="8.86328125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.86328125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1861,7 +2081,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1869,9 +2089,9 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -1879,45 +2099,45 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C5" s="10">
         <v>7024640</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>72</v>
+        <v>62</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>68</v>
       </c>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -1925,7 +2145,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1933,19 +2153,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1953,9 +2173,9 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B10" s="12">
         <v>4</v>
@@ -1965,7 +2185,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1973,9 +2193,9 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" s="13">
         <v>45730</v>
@@ -1985,9 +2205,9 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" s="13">
         <v>45831</v>
@@ -1997,7 +2217,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -2005,21 +2225,21 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" s="12">
         <v>5</v>
@@ -2029,7 +2249,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2037,7 +2257,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -2045,19 +2265,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -2065,9 +2285,9 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A21" s="14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2075,9 +2295,9 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="6"/>
@@ -2085,9 +2305,9 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="6"/>
@@ -2095,7 +2315,7 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
       <c r="B24" s="8"/>
       <c r="C24" s="6"/>
@@ -2103,29 +2323,29 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -2133,31 +2353,31 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2165,7 +2385,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2173,9 +2393,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2183,9 +2403,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -2193,9 +2413,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -2203,9 +2423,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -2213,7 +2433,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -2221,9 +2441,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A37" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -2231,43 +2451,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2275,7 +2495,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2283,7 +2503,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2291,9 +2511,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A44" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -2301,43 +2521,37 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>48</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B45" s="8"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>49</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B46" s="8"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>50</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B47" s="8"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2345,7 +2559,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2353,13 +2567,11 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>52</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B50" s="8"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -2386,19 +2598,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.42578125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="29.3984375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.86328125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.86328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.3984375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.3984375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.86328125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.3984375" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.3984375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2406,7 +2618,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2414,9 +2626,9 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2424,45 +2636,45 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C5" s="10">
         <v>7024769</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -2470,7 +2682,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2478,19 +2690,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -2498,9 +2710,9 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B10" s="12">
         <v>4</v>
@@ -2510,7 +2722,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -2518,9 +2730,9 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" s="13">
         <v>45730</v>
@@ -2530,9 +2742,9 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" s="13">
         <v>45831</v>
@@ -2542,7 +2754,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -2550,21 +2762,21 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" s="12">
         <v>5</v>
@@ -2574,7 +2786,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2582,7 +2794,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -2590,19 +2802,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -2610,9 +2822,9 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A21" s="14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2620,31 +2832,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2652,29 +2864,29 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -2682,31 +2894,31 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2714,7 +2926,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2722,9 +2934,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2732,9 +2944,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -2742,9 +2954,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -2752,9 +2964,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -2762,7 +2974,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -2770,9 +2982,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A37" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -2780,43 +2992,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2824,7 +3036,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2832,7 +3044,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2840,9 +3052,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A44" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -2850,43 +3062,37 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>48</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B45" s="8"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>49</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B46" s="8"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>50</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B47" s="8"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2894,7 +3100,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2902,13 +3108,11 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>52</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B50" s="8"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -2935,19 +3139,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC551AE2-232B-4F37-A6D5-76CE042A5043}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.42578125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="29.3984375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.86328125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.86328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.3984375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.3984375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.86328125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.3984375" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.3984375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2955,7 +3159,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2963,9 +3167,9 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2973,45 +3177,45 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C5" s="10">
         <v>7024749</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>71</v>
+        <v>86</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>67</v>
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -3019,7 +3223,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3027,19 +3231,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -3047,9 +3251,9 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B10" s="12">
         <v>4</v>
@@ -3059,7 +3263,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -3067,9 +3271,9 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" s="13">
         <v>45730</v>
@@ -3079,9 +3283,9 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" s="13">
         <v>45831</v>
@@ -3091,7 +3295,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -3099,21 +3303,21 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" s="12">
         <v>5</v>
@@ -3123,7 +3327,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -3131,7 +3335,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -3139,19 +3343,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3159,9 +3363,9 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A21" s="14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -3169,31 +3373,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3201,29 +3405,29 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -3231,31 +3435,31 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -3263,7 +3467,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -3271,9 +3475,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -3281,9 +3485,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -3291,9 +3495,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -3301,9 +3505,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -3311,7 +3515,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -3319,9 +3523,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A37" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -3329,43 +3533,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3373,7 +3577,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -3381,7 +3585,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -3389,9 +3593,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A44" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3399,43 +3603,37 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>48</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B45" s="8"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>49</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B46" s="8"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>50</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B47" s="8"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -3443,7 +3641,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3451,13 +3649,11 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>52</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B50" s="8"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -3484,19 +3680,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{283BD7E5-E0D0-4A6A-B1D5-0C7015D88B45}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.42578125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="29.3984375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.86328125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.86328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.3984375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.3984375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.86328125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.3984375" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.3984375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3504,7 +3700,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3512,9 +3708,9 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3522,45 +3718,45 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C5" s="10">
         <v>7025068</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>70</v>
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -3568,7 +3764,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3576,19 +3772,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -3596,9 +3792,9 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B10" s="12">
         <v>4</v>
@@ -3608,7 +3804,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -3616,9 +3812,9 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" s="13">
         <v>45730</v>
@@ -3628,9 +3824,9 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" s="13">
         <v>45831</v>
@@ -3640,7 +3836,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -3648,21 +3844,21 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" s="12">
         <v>5</v>
@@ -3672,7 +3868,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -3680,7 +3876,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -3688,19 +3884,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3708,9 +3904,9 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A21" s="14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -3718,31 +3914,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3750,29 +3946,29 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -3780,31 +3976,31 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -3812,7 +4008,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -3820,9 +4016,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -3830,9 +4026,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -3840,9 +4036,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -3850,9 +4046,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -3860,7 +4056,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -3868,9 +4064,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A37" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -3878,43 +4074,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3922,7 +4118,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -3930,7 +4126,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -3938,9 +4134,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A44" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3948,43 +4144,37 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>48</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B45" s="8"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>49</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B46" s="8"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>50</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B47" s="8"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -3992,7 +4182,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -4000,13 +4190,11 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>52</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B50" s="8"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -4033,19 +4221,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB98D58-38D8-4A44-9926-B20EEA7E6B71}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.42578125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="29.3984375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.86328125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.86328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.3984375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.3984375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.86328125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.3984375" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.3984375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4053,7 +4241,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -4061,9 +4249,9 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -4071,47 +4259,47 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="10">
         <v>7024847</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -4119,7 +4307,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4127,19 +4315,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -4147,9 +4335,9 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B10" s="12">
         <v>4</v>
@@ -4159,7 +4347,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4167,9 +4355,9 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" s="13">
         <v>45730</v>
@@ -4179,9 +4367,9 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" s="13">
         <v>45831</v>
@@ -4191,7 +4379,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -4199,21 +4387,21 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" s="12">
         <v>5</v>
@@ -4223,7 +4411,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -4231,7 +4419,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -4239,19 +4427,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -4259,9 +4447,9 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A21" s="14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -4269,31 +4457,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -4301,29 +4489,29 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -4331,31 +4519,31 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4363,7 +4551,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -4371,9 +4559,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -4381,9 +4569,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -4391,9 +4579,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -4401,9 +4589,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -4411,7 +4599,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -4419,9 +4607,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A37" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -4429,43 +4617,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -4473,7 +4661,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -4481,7 +4669,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -4489,9 +4677,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A44" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -4499,43 +4687,37 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>48</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B45" s="8"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>49</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B46" s="8"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>50</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B47" s="8"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -4543,7 +4725,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -4551,13 +4733,11 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>52</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B50" s="8"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -4585,17 +4765,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="5" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" style="5" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="29.1328125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="49.73046875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.3984375" style="5" customWidth="1"/>
+    <col min="4" max="5" width="16.1328125" style="5" customWidth="1"/>
+    <col min="6" max="7" width="11.3984375" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.3984375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4603,7 +4783,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -4611,9 +4791,9 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -4621,32 +4801,32 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C5" s="10">
         <v>1234567</v>
@@ -4655,7 +4835,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -4663,7 +4843,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4671,9 +4851,9 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -4681,7 +4861,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -4689,9 +4869,9 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B10" s="12">
         <v>7</v>
@@ -4701,7 +4881,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4709,9 +4889,9 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" s="13">
         <v>45351</v>
@@ -4721,9 +4901,9 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" s="13">
         <v>45594</v>
@@ -4733,7 +4913,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -4741,9 +4921,9 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -4751,19 +4931,19 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -4771,7 +4951,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -4779,19 +4959,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -4799,9 +4979,9 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A21" s="14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -4809,31 +4989,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -4841,63 +5021,63 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
       <c r="B27" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4905,7 +5085,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -4913,9 +5093,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -4923,43 +5103,43 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -4967,9 +5147,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A37" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -4977,43 +5157,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -5021,7 +5201,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -5029,7 +5209,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -5037,9 +5217,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A44" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -5047,43 +5227,43 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -5091,7 +5271,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -5099,12 +5279,12 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>

--- a/LaTeXTemplate/author.xlsx
+++ b/LaTeXTemplate/author.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlm\Documents\LaTeXTemplate\LaTeXTemplate\LaTeXTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ninab\Documents\Studium\Semester_4\AT\eigeneSammlung\LaTeXTemplate\LaTeXTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6444497F-2358-424D-AB92-F4AB7D76A196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17913A02-EDB0-4838-B857-D06D17E552E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,13 @@
     <sheet name="Student 3" sheetId="8" r:id="rId5"/>
     <sheet name="Student 4" sheetId="7" r:id="rId6"/>
     <sheet name="Student 5" sheetId="9" r:id="rId7"/>
-    <sheet name="wings" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="81">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -107,9 +106,6 @@
     <t>Company name/Department:</t>
   </si>
   <si>
-    <t>&lt;Mechanical Engineering Department&gt;</t>
-  </si>
-  <si>
     <t>Street Workplace:</t>
   </si>
   <si>
@@ -119,28 +115,16 @@
     <t>City Workplace:</t>
   </si>
   <si>
-    <t>&lt;26723 Emden&gt;</t>
-  </si>
-  <si>
     <t>Telephone:</t>
   </si>
   <si>
     <t xml:space="preserve">Home: </t>
   </si>
   <si>
-    <t>&lt;04921 123 456&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Study: </t>
   </si>
   <si>
-    <t>&lt;04921 807 1429&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Workplace: </t>
-  </si>
-  <si>
-    <t>&lt;04921 807 1428&gt;</t>
   </si>
   <si>
     <t>Supervisor workplace:</t>
@@ -172,49 +156,13 @@
     <t>Second examiner:</t>
   </si>
   <si>
-    <t>&lt;Prof. Dr. Carla Columna&gt;</t>
-  </si>
-  <si>
-    <t>&lt;00494921 807-1001&gt;</t>
-  </si>
-  <si>
-    <t>&lt;albert.einstein@hs-emden-leer.de&gt;</t>
-  </si>
-  <si>
     <t>Outstanding examinations:</t>
   </si>
   <si>
-    <t>&lt;GDV, QS, QM&gt;</t>
-  </si>
-  <si>
     <t>Student 2</t>
   </si>
   <si>
-    <t>&lt;Hochschule Emden/Leer&gt; or &lt; VW Wolfsburg&gt; or &lt;...&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Fachbereich Technik&gt;  or &lt;Strak&gt; or &lt;...&gt;</t>
-  </si>
-  <si>
     <t>Student 3</t>
-  </si>
-  <si>
-    <t>Wings</t>
-  </si>
-  <si>
-    <t>Elmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> &lt;5&gt; or &lt;10&gt;</t>
-  </si>
-  <si>
-    <t>&lt;01.01.2000&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Steinweg 15&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Einstein, Albert&gt;</t>
   </si>
   <si>
     <t>Carl Lewis</t>
@@ -648,22 +596,16 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -673,9 +615,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -705,8 +653,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
@@ -1835,20 +1783,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="12.95" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="12.9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="4" width="30.59765625" customWidth="1"/>
+    <col min="2" max="4" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="17" t="s">
+    <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-    </row>
-    <row r="7" spans="2:4" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+    </row>
+    <row r="7" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1859,14 +1807,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
         <v>5</v>
@@ -1875,14 +1823,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
         <v>5</v>
@@ -1891,36 +1839,36 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="2:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1940,104 +1888,104 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.86328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.3984375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="34.9296875" style="5" customWidth="1"/>
-    <col min="4" max="6" width="11.3984375" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="11.3984375" style="5"/>
+    <col min="1" max="1" width="24.88671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" style="5" customWidth="1"/>
+    <col min="4" max="6" width="11.44140625" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="61.9" customHeight="1" x14ac:dyDescent="1">
+    <row r="1" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A1" s="25" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="27"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="21"/>
-    </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="21"/>
-    </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D1" s="19"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="17"/>
+    </row>
+    <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="17"/>
+    </row>
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="B4" s="32"/>
       <c r="C4" s="33"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
-    </row>
-    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="21"/>
-    </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D4" s="19"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="35"/>
       <c r="C6" s="36"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="21"/>
-    </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D6" s="19"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="37" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B7" s="38"/>
       <c r="C7" s="39"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="21"/>
-    </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="21"/>
-    </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="21"/>
-    </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="21"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="17"/>
+    </row>
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2062,18 +2010,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.265625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.86328125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="33.1328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="16.1328125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="43.86328125" style="5" customWidth="1"/>
-    <col min="6" max="7" width="8.86328125" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.86328125" style="5"/>
+    <col min="1" max="1" width="47.21875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="43.88671875" style="5" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2081,7 +2029,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2089,7 +2037,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
@@ -2099,7 +2047,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
@@ -2119,25 +2067,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C5" s="10">
         <v>7024640</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -2145,7 +2093,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2153,19 +2101,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -2173,7 +2121,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -2185,7 +2133,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -2193,7 +2141,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>17</v>
       </c>
@@ -2205,7 +2153,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>18</v>
       </c>
@@ -2217,7 +2165,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -2225,19 +2173,19 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
@@ -2249,7 +2197,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2257,7 +2205,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -2265,19 +2213,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -2285,7 +2233,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>22</v>
       </c>
@@ -2295,27 +2243,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="8"/>
+      <c r="B22" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="8"/>
+      <c r="B23" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="8"/>
       <c r="C24" s="6"/>
@@ -2323,29 +2275,29 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -2353,31 +2305,31 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2385,7 +2337,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2393,9 +2345,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2403,9 +2355,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -2413,9 +2365,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -2423,9 +2375,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -2433,7 +2385,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -2441,9 +2393,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="14" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -2451,43 +2403,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2495,7 +2447,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2503,7 +2455,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2511,9 +2463,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -2521,37 +2473,43 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2559,7 +2517,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2567,9 +2525,9 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="6"/>
@@ -2598,19 +2556,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.3984375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.86328125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.86328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.3984375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.3984375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.86328125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.3984375" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.3984375" style="5"/>
+    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2618,7 +2576,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2626,7 +2584,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
@@ -2636,7 +2594,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
@@ -2656,25 +2614,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C5" s="10">
         <v>7024769</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -2682,7 +2640,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2690,19 +2648,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -2710,7 +2668,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -2722,7 +2680,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -2730,7 +2688,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>17</v>
       </c>
@@ -2742,7 +2700,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>18</v>
       </c>
@@ -2754,7 +2712,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -2762,19 +2720,19 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
@@ -2786,7 +2744,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2794,7 +2752,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -2802,19 +2760,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -2822,7 +2780,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>22</v>
       </c>
@@ -2832,31 +2790,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2864,29 +2822,29 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -2894,31 +2852,31 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2926,7 +2884,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2934,9 +2892,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2944,9 +2902,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -2954,9 +2912,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -2964,9 +2922,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -2974,7 +2932,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -2982,9 +2940,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="14" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -2992,43 +2950,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3036,7 +2994,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -3044,7 +3002,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -3052,9 +3010,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3062,37 +3020,43 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -3100,7 +3064,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3108,9 +3072,9 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="6"/>
@@ -3139,19 +3103,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC551AE2-232B-4F37-A6D5-76CE042A5043}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.3984375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.86328125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.86328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.3984375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.3984375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.86328125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.3984375" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.3984375" style="5"/>
+    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3159,7 +3123,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3167,7 +3131,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
@@ -3177,7 +3141,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
@@ -3197,25 +3161,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C5" s="10">
         <v>7024749</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -3223,7 +3187,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3231,19 +3195,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -3251,7 +3215,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -3263,7 +3227,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -3271,7 +3235,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>17</v>
       </c>
@@ -3283,7 +3247,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>18</v>
       </c>
@@ -3295,7 +3259,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -3303,19 +3267,19 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
@@ -3327,7 +3291,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -3335,7 +3299,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -3343,19 +3307,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3363,7 +3327,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>22</v>
       </c>
@@ -3373,31 +3337,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3405,29 +3369,29 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -3435,31 +3399,31 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -3467,7 +3431,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -3475,9 +3439,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -3485,9 +3449,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -3495,9 +3459,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -3505,9 +3469,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -3515,7 +3479,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -3523,9 +3487,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="14" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -3533,43 +3497,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3577,7 +3541,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -3585,7 +3549,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -3593,9 +3557,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3603,37 +3567,43 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -3641,7 +3611,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3649,9 +3619,9 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="6"/>
@@ -3680,19 +3650,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{283BD7E5-E0D0-4A6A-B1D5-0C7015D88B45}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.3984375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.86328125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.86328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.3984375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.3984375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.86328125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.3984375" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.3984375" style="5"/>
+    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3700,7 +3670,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3708,7 +3678,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
@@ -3718,7 +3688,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
@@ -3738,25 +3708,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C5" s="10">
         <v>7025068</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -3764,7 +3734,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3772,19 +3742,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -3792,7 +3762,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -3804,7 +3774,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -3812,7 +3782,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>17</v>
       </c>
@@ -3824,7 +3794,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>18</v>
       </c>
@@ -3836,7 +3806,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -3844,19 +3814,19 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
@@ -3868,7 +3838,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -3876,7 +3846,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -3884,19 +3854,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3904,7 +3874,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>22</v>
       </c>
@@ -3914,31 +3884,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3946,29 +3916,29 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -3976,31 +3946,31 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4008,7 +3978,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -4016,9 +3986,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -4026,9 +3996,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -4036,9 +4006,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -4046,9 +4016,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -4056,7 +4026,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -4064,9 +4034,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="14" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -4074,43 +4044,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -4118,7 +4088,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -4126,7 +4096,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -4134,9 +4104,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -4144,37 +4114,43 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -4182,7 +4158,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -4190,9 +4166,9 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="6"/>
@@ -4221,19 +4197,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB98D58-38D8-4A44-9926-B20EEA7E6B71}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.3984375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="46.86328125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.86328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.3984375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="44.3984375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.86328125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.3984375" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.3984375" style="5"/>
+    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4241,7 +4217,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -4249,7 +4225,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="3" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
@@ -4259,7 +4235,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
@@ -4279,27 +4255,27 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C5" s="10">
         <v>7024847</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="11"/>
@@ -4307,7 +4283,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4315,19 +4291,19 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -4335,7 +4311,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
@@ -4347,7 +4323,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4355,7 +4331,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>17</v>
       </c>
@@ -4367,7 +4343,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>18</v>
       </c>
@@ -4379,7 +4355,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -4387,19 +4363,19 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
@@ -4411,7 +4387,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -4419,7 +4395,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -4427,19 +4403,19 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -4447,7 +4423,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>22</v>
       </c>
@@ -4457,31 +4433,31 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -4489,29 +4465,29 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="8" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6"/>
@@ -4519,31 +4495,31 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4551,7 +4527,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -4559,9 +4535,9 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -4569,9 +4545,9 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="6"/>
@@ -4579,9 +4555,9 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="6"/>
@@ -4589,9 +4565,9 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="6"/>
@@ -4599,7 +4575,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -4607,9 +4583,9 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="14" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -4617,43 +4593,43 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -4661,7 +4637,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="15"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -4669,7 +4645,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -4677,9 +4653,9 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -4687,37 +4663,43 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -4725,7 +4707,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -4733,9 +4715,9 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="6"/>
@@ -4760,547 +4742,4 @@
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="29.1328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="49.73046875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.3984375" style="5" customWidth="1"/>
-    <col min="4" max="5" width="16.1328125" style="5" customWidth="1"/>
-    <col min="6" max="7" width="11.3984375" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="11.3984375" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1234567</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="12">
-        <v>7</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="13">
-        <v>45351</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="13">
-        <v>45594</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A21" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-    </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="15"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A37" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-    </row>
-    <row r="38" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-    </row>
-    <row r="40" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-    </row>
-    <row r="41" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="15"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="15"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-    </row>
-    <row r="43" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="15"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="44" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A44" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-    </row>
-    <row r="46" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-    </row>
-    <row r="47" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-    </row>
-    <row r="48" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="15"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="15"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-    </row>
-    <row r="50" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Technical Management,Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.78740200000000005" bottom="0.78740200000000005" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-  <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>